--- a/template/event-inviter-template.xlsx
+++ b/template/event-inviter-template.xlsx
@@ -520,16 +520,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,6 +583,81 @@
           <t>Receivers</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Hijri Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Shamsi Date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Day of Week</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fajr Time</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Dhuhr Time</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Maghrib Time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Show Gregorian In Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Show Hijri In Email</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Show Shamsi In Email</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Show Day Of Week In Email</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Show Fajr In Email</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Show Dhuhr In Email</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Show Maghrib In Email</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Sender Name</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -582,25 +672,24 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>۱۹:۴۵ تا ۲۰:۳۰ - قرائت قرآن و تفسیر آیات ۲۱ تا ۲۶ سوره توبه
-۲۰:۳۰ تا ۲۰:۵۰ - پذیرایی
-۲۰:۵۰ تا ۲۱:۳۰ - ادامه ی تفسیر
-۲۱:۳۰ تا ۲۱:۴۵ - نماز جماعت (MC 2018)</t>
+          <t>۱۹:۴۵ - ۲۰:۳۰ - قرائت قرآن و تفسیر آیات ۲۱ تا ۲۶ سوره توبه (MC 2018)
+۲۰:۳۰ - ۲۰:۵۰ - پذیرایی (MC 2018)
+۲۰:۵۰ - ۲۱:۳۰ - ادامه ی تفسیر (MC 2018)
+۲۱:۳۰ - ۲۱:۴۵ - نماز جماعت (MC 2018)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>[جدول جلسات هفتگی قرآن: &lt;insert your schedule link here&gt;]
-ایمیل ارتباطی: uwq.mo...@gmail.com</t>
+          <t>لطفاً به موقع حضور یابید.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>رَبِّ اجْعَلْنِی مُقیمَ الصَّلاةِ وَمِن ذُرِّيَتِی ـ رَبَّنَا وَتَقَبَّل دُعَاءِ ﴾ابراهیم-۴۰﴿
+          <t>رَبِّ اجْعَلْنِی مُقیمَ الصَّلاةِ وَمِن ذُرِّيَتِی ـ رَبَّنَا وَتَقَبَّل دُعَاءِ ﴾ابراهیم-۴۰﴿
 پروردگارا، مرا برپادارنده نماز قرار ده، و از فرزندان من نیز. پروردگارا، و دعای مرا بپذیر.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>جدول جلسات هفتگی: &lt;insert your schedule link here&gt;</t>
         </is>
@@ -608,6 +697,67 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>uw_q...@googlegroups.com</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>۱۸ محرم ۱۴۴۸</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>۱۲ تیر ۱۴۰۵</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>جمعه (Friday)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>۰۳:۳۱</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>۱۳:۲۷</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>۲۱:۳۱</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>جلسه قرآن دانشگاه واترلو (University of Waterloo Quran Session)</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>با تشکر از حضور شما، منتظر دیدارتان هستیم.</t>
         </is>
       </c>
     </row>
